--- a/data/trans_orig/P36BPD04_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023</t>
+          <t>Población según la frecuencia de consumo de fruta o zumos naturales en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47236</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48261</t>
+          <t>51645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80774</t>
+          <t>84916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71337</t>
+          <t>71351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132797</t>
+          <t>136636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56577</t>
+          <t>57577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97808</t>
+          <t>94414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139386</t>
+          <t>137917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213155</t>
+          <t>214199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177010</t>
+          <t>179655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>245014</t>
+          <t>247513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131197</t>
+          <t>130773</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178388</t>
+          <t>178382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>325118</t>
+          <t>321695</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>406654</t>
+          <t>407322</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>39048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94293</t>
+          <t>94082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35386</t>
+          <t>36451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73246</t>
+          <t>73787</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87345</t>
+          <t>86432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152983</t>
+          <t>152789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28778</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65812</t>
+          <t>65327</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50169</t>
+          <t>48011</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>60525</t>
+          <t>58972</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106937</t>
+          <t>106129</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76364</t>
+          <t>75117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120046</t>
+          <t>117844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56250</t>
+          <t>54627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114791</t>
+          <t>113147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142597</t>
+          <t>141679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221837</t>
+          <t>219968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191329</t>
+          <t>191360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244599</t>
+          <t>243554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>281699</t>
+          <t>283494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>402790</t>
+          <t>392707</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>490691</t>
+          <t>489482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632009</t>
+          <t>634155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>86317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>40638</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87000</t>
+          <t>86012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98478</t>
+          <t>96999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>159094</t>
+          <t>162513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21351</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44661</t>
+          <t>47123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39710</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47662</t>
+          <t>49206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78211</t>
+          <t>79455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92383</t>
+          <t>92149</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131171</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77542</t>
+          <t>78789</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>107206</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178704</t>
+          <t>179545</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>228308</t>
+          <t>227322</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>275885</t>
+          <t>274380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>321601</t>
+          <t>323005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303058</t>
+          <t>302591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>341321</t>
+          <t>340505</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>591005</t>
+          <t>590037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>648343</t>
+          <t>650236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78545</t>
+          <t>77524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116150</t>
+          <t>114636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83961</t>
+          <t>84189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113325</t>
+          <t>113000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170849</t>
+          <t>170346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219097</t>
+          <t>216925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87198</t>
+          <t>82251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>28443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>48403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54678</t>
+          <t>56110</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121205</t>
+          <t>122762</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>53480</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178013</t>
+          <t>180392</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86968</t>
+          <t>86543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120504</t>
+          <t>120556</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132340</t>
+          <t>146422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>278032</t>
+          <t>281692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>445942</t>
+          <t>448502</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>752212</t>
+          <t>758961</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>330749</t>
+          <t>331773</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>420186</t>
+          <t>423236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>842339</t>
+          <t>835541</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1253833</t>
+          <t>1190802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64084</t>
+          <t>55529</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197667</t>
+          <t>198509</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143594</t>
+          <t>143146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>274386</t>
+          <t>263329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190777</t>
+          <t>191969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398935</t>
+          <t>396542</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>39161</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42729</t>
+          <t>44525</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68308</t>
+          <t>69345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>77542</t>
+          <t>78537</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109985</t>
+          <t>110376</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60189</t>
+          <t>60305</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83878</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145148</t>
+          <t>147634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185702</t>
+          <t>186942</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>310044</t>
+          <t>309831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>354285</t>
+          <t>353110</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>318318</t>
+          <t>319286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>352191</t>
+          <t>353174</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>638297</t>
+          <t>639248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>694161</t>
+          <t>690811</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,37%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86081</t>
+          <t>91482</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>126192</t>
+          <t>129022</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>98721</t>
+          <t>98496</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>126748</t>
+          <t>128365</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>198532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>243867</t>
+          <t>241126</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>24268</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>441602</t>
+          <t>441758</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>30381</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>570503</t>
+          <t>606114</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42309</t>
+          <t>42856</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64055</t>
+          <t>65244</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67959</t>
+          <t>66721</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53890</t>
+          <t>47653</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>127281</t>
+          <t>126544</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>189010</t>
+          <t>190199</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>220467</t>
+          <t>221239</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>96548</t>
+          <t>94277</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>350286</t>
+          <t>348260</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>230274</t>
+          <t>215892</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>556766</t>
+          <t>553764</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>79762</t>
+          <t>79497</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>107057</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>50396</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>192264</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>120258</t>
+          <t>101566</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>280234</t>
+          <t>278995</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>10071</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26593</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>45340</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>46900</t>
+          <t>47173</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>68134</t>
+          <t>68107</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>78094</t>
+          <t>78969</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>104806</t>
+          <t>106239</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>163927</t>
+          <t>163876</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>189723</t>
+          <t>189942</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>250677</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>280030</t>
+          <t>280257</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>424459</t>
+          <t>423866</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>462947</t>
+          <t>462775</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>55003</t>
+          <t>54870</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>77431</t>
+          <t>78005</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>80546</t>
+          <t>80738</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>104196</t>
+          <t>104615</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>142252</t>
+          <t>143050</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>175554</t>
+          <t>177466</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>160937</t>
+          <t>158122</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>254177</t>
+          <t>247224</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>180996</t>
+          <t>181595</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>993277</t>
+          <t>1118414</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>383053</t>
+          <t>379476</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1295234</t>
+          <t>1380234</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>472190</t>
+          <t>467138</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>682254</t>
+          <t>674007</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>431420</t>
+          <t>435251</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>581725</t>
+          <t>583919</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>975893</t>
+          <t>974631</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1230057</t>
+          <t>1244859</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1877395</t>
+          <t>1894690</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2302735</t>
+          <t>2369611</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1653151</t>
+          <t>1615310</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2176957</t>
+          <t>2174129</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3720029</t>
+          <t>3688216</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4317148</t>
+          <t>4347843</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>484201</t>
+          <t>489481</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>696220</t>
+          <t>694271</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>594530</t>
+          <t>607721</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>812627</t>
+          <t>812179</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1177004</t>
+          <t>1157964</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1466550</t>
+          <t>1480467</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD04_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD04_2023-Edad-trans_orig.xlsx
@@ -725,17 +725,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45554</t>
+          <t>47131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51645</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56156</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37869</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84916</t>
+          <t>83545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>99113</t>
+          <t>94992</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71351</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136636</t>
+          <t>124300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>81140</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57577</t>
+          <t>62528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94414</t>
+          <t>103978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>174105</t>
+          <t>176131</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137917</t>
+          <t>144234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214199</t>
+          <t>211828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>213664</t>
+          <t>209647</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179655</t>
+          <t>179336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>247513</t>
+          <t>241005</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153981</t>
+          <t>185755</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130773</t>
+          <t>160075</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178382</t>
+          <t>211403</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>367645</t>
+          <t>395402</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>321695</t>
+          <t>352522</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>407322</t>
+          <t>435392</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61504</t>
+          <t>76949</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>52211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94082</t>
+          <t>106162</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53777</t>
+          <t>61948</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36451</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73787</t>
+          <t>84728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>115281</t>
+          <t>138897</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86432</t>
+          <t>108663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152789</t>
+          <t>180574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45434</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65327</t>
+          <t>67995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35069</t>
+          <t>36698</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48011</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>80504</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>66466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>106129</t>
+          <t>109793</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96111</t>
+          <t>99516</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75117</t>
+          <t>78738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117844</t>
+          <t>123226</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89315</t>
+          <t>95158</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54627</t>
+          <t>77330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113147</t>
+          <t>115978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>185426</t>
+          <t>194674</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141679</t>
+          <t>166765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219968</t>
+          <t>224709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>217603</t>
+          <t>250312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191360</t>
+          <t>222967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243554</t>
+          <t>279158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>321451</t>
+          <t>293983</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283494</t>
+          <t>269655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>392707</t>
+          <t>317631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>539053</t>
+          <t>544295</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>489482</t>
+          <t>507943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>634155</t>
+          <t>580437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64399</t>
+          <t>78958</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47091</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86317</t>
+          <t>104724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65669</t>
+          <t>75245</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40638</t>
+          <t>56259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86012</t>
+          <t>94039</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>130068</t>
+          <t>154203</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96999</t>
+          <t>126866</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>162513</t>
+          <t>184837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>33743</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21597</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>48573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30167</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>24787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>44720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>61718</t>
+          <t>67644</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>53944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79455</t>
+          <t>85661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>110687</t>
+          <t>123973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92149</t>
+          <t>104088</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130995</t>
+          <t>148444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91494</t>
+          <t>102468</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78789</t>
+          <t>86836</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>107135</t>
+          <t>119454</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>202181</t>
+          <t>226441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>179545</t>
+          <t>200519</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>227322</t>
+          <t>254226</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>299152</t>
+          <t>345520</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>274380</t>
+          <t>320553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>323005</t>
+          <t>373119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>322469</t>
+          <t>367434</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>302591</t>
+          <t>345519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340505</t>
+          <t>387807</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>621620</t>
+          <t>712954</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>590037</t>
+          <t>679407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>650236</t>
+          <t>747129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,16%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>116483</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77524</t>
+          <t>95230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114636</t>
+          <t>139131</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>98338</t>
+          <t>118335</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84189</t>
+          <t>102691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113000</t>
+          <t>135177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>193123</t>
+          <t>234819</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170346</t>
+          <t>205448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216925</t>
+          <t>262615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52008</t>
+          <t>49122</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82251</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>42615</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28443</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48403</t>
+          <t>52950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>91737</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56110</t>
+          <t>74209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122762</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>127776</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53480</t>
+          <t>107629</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180392</t>
+          <t>150352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>104062</t>
+          <t>111264</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86543</t>
+          <t>96965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>120556</t>
+          <t>128451</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>226130</t>
+          <t>239040</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>146422</t>
+          <t>214418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>281692</t>
+          <t>266756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>577633</t>
+          <t>369331</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>448502</t>
+          <t>344102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>758961</t>
+          <t>398583</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>394410</t>
+          <t>431763</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>331773</t>
+          <t>410463</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>423236</t>
+          <t>452073</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>972043</t>
+          <t>801094</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>835541</t>
+          <t>767544</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1190802</t>
+          <t>831877</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>136077</t>
+          <t>154388</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55529</t>
+          <t>130874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198509</t>
+          <t>177909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>175476</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>143146</t>
+          <t>134037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>263329</t>
+          <t>168628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>311553</t>
+          <t>304681</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>191969</t>
+          <t>274765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>396542</t>
+          <t>332025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711952</t>
+          <t>735936</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711952</t>
+          <t>735936</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711952</t>
+          <t>735936</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1599738</t>
+          <t>1436553</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1599738</t>
+          <t>1436553</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1599738</t>
+          <t>1436553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39161</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26968</t>
+          <t>29572</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>22120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>59163</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44525</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>69345</t>
+          <t>75458</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>92729</t>
+          <t>96317</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78537</t>
+          <t>79219</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110376</t>
+          <t>114056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60305</t>
+          <t>67813</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84270</t>
+          <t>93710</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>164288</t>
+          <t>175525</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147634</t>
+          <t>153724</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186942</t>
+          <t>197997</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>331328</t>
+          <t>360380</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>309831</t>
+          <t>336084</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>353110</t>
+          <t>382707</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>336161</t>
+          <t>368948</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>319286</t>
+          <t>350721</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>353174</t>
+          <t>387032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>667490</t>
+          <t>729328</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>639248</t>
+          <t>701428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>690811</t>
+          <t>762317</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,66%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>108029</t>
+          <t>121977</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91482</t>
+          <t>103446</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129022</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>112713</t>
+          <t>130588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>98496</t>
+          <t>116519</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>128365</t>
+          <t>148692</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>220742</t>
+          <t>252565</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>198532</t>
+          <t>227871</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>241126</t>
+          <t>277830</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547402</t>
+          <t>608316</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547402</t>
+          <t>608316</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547402</t>
+          <t>608316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1107606</t>
+          <t>1216581</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1107606</t>
+          <t>1216581</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1107606</t>
+          <t>1216581</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>214996</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>441758</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>231814</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>606114</t>
+          <t>41572</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53143</t>
+          <t>59022</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42856</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65244</t>
+          <t>72684</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>36639</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>95293</t>
+          <t>103841</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>47653</t>
+          <t>89279</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>126544</t>
+          <t>118989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -3796,102 +3796,102 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>205314</t>
+          <t>224438</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>190199</t>
+          <t>206034</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>221239</t>
+          <t>240479</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>55,13%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>59,07%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>246581</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>231214</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>261661</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>56,36%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>52,85%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>59,81%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>471019</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>447248</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>493051</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>55,77%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>60,09%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>226697</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>94277</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>348260</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>432011</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>215892</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>553764</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>44,31%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>92891</t>
+          <t>105065</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>79497</t>
+          <t>91293</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107057</t>
+          <t>122149</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>122864</t>
+          <t>133317</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>50396</t>
+          <t>120032</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>192264</t>
+          <t>146457</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>215755</t>
+          <t>238382</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>101566</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>278995</t>
+          <t>259810</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>606707</t>
+          <t>437482</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>606707</t>
+          <t>437482</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>606707</t>
+          <t>437482</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>974873</t>
+          <t>844562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>974873</t>
+          <t>844562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>974873</t>
+          <t>844562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10071</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>34718</t>
+          <t>36050</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>45340</t>
+          <t>46740</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>56993</t>
+          <t>59788</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>47173</t>
+          <t>49804</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>68107</t>
+          <t>70585</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>95838</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>78969</t>
+          <t>82039</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>106239</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>177150</t>
+          <t>195324</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>163876</t>
+          <t>180810</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>189942</t>
+          <t>208709</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,17 +4400,17 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>265795</t>
+          <t>290053</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>251560</t>
+          <t>274661</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>280257</t>
+          <t>304826</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,22 +4435,22 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>442945</t>
+          <t>485377</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>423866</t>
+          <t>463515</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>462775</t>
+          <t>505652</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,3%</t>
         </is>
       </c>
     </row>
@@ -4478,67 +4478,67 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>73903</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>62869</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>78005</t>
+          <t>86871</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>20,27%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>28,01%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>102549</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>90124</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>116665</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>22,09%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>19,41%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>92300</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>80738</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>104615</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>158454</t>
+          <t>176452</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>143050</t>
+          <t>160108</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>177466</t>
+          <t>195307</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425439</t>
+          <t>464209</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425439</t>
+          <t>464209</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425439</t>
+          <t>464209</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708198</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708198</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708198</t>
+          <t>774407</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>204371</t>
+          <t>210241</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>158122</t>
+          <t>179966</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>247224</t>
+          <t>245850</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>386008</t>
+          <t>201038</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>181595</t>
+          <t>176869</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1118414</t>
+          <t>230049</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>590379</t>
+          <t>411279</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>379476</t>
+          <t>370773</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1380234</t>
+          <t>459581</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>608570</t>
+          <t>637646</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>467138</t>
+          <t>587398</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>674007</t>
+          <t>691396</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>530565</t>
+          <t>573844</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>435251</t>
+          <t>536409</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>583919</t>
+          <t>621771</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1139135</t>
+          <t>1211491</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>1150027</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1244859</t>
+          <t>1281819</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2021844</t>
+          <t>1954952</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1894690</t>
+          <t>1895314</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2369611</t>
+          <t>2032830</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2020963</t>
+          <t>2184519</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1615310</t>
+          <t>2127672</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2174129</t>
+          <t>2236697</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>4042807</t>
+          <t>4139471</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3688216</t>
+          <t>4048611</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4347843</t>
+          <t>4219216</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>623839</t>
+          <t>727723</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>489481</t>
+          <t>675106</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>694271</t>
+          <t>781812</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>721136</t>
+          <t>772276</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>607721</t>
+          <t>730472</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>812179</t>
+          <t>815131</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1344975</t>
+          <t>1499999</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1157964</t>
+          <t>1434999</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1480467</t>
+          <t>1574613</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3458624</t>
+          <t>3530562</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3658672</t>
+          <t>3731678</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7117296</t>
+          <t>7262240</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
